--- a/ml_pipeline/Bang_5.5_Template_6vong.xlsx
+++ b/ml_pipeline/Bang_5.5_Template_6vong.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DATN\ml_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869FD4E6-0F4F-4B81-A8E5-94B937C66AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77727DB4-017F-4A73-84BC-E70EB749EB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2292" yWindow="2520" windowWidth="17172" windowHeight="10764" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Huong_dan" sheetId="1" r:id="rId1"/>
@@ -79,9 +79,6 @@
     <t>user1, user14, user18, user23, user26</t>
   </si>
   <si>
-    <t>KHỐI 1 — EER tập mở (open-set, từ bảng OPEN-SET cột EER, dạng 0–1)</t>
-  </si>
-  <si>
     <t>Hàm quyết định</t>
   </si>
   <si>
@@ -109,12 +106,6 @@
     <t>maha</t>
   </si>
   <si>
-    <t>KHỐI 2 — EER tập đóng (closed-set, từ bảng CLOSED-SET cột EER, dạng 0–1)</t>
-  </si>
-  <si>
-    <t>KHỐI 3 — AUC tập mở (open-set, từ bảng OPEN-SET cột AUC, dạng 0–1)</t>
-  </si>
-  <si>
     <t>Template thống kê Bảng 5.5 — kiểm thử chéo 6 vòng (leave-users-out)</t>
   </si>
   <si>
@@ -200,6 +191,15 @@
   </si>
   <si>
     <t>HELD_OUT_IDS theo từng vòng:</t>
+  </si>
+  <si>
+    <t>KHỐI 1 — EER tập mở</t>
+  </si>
+  <si>
+    <t>KHỐI 2 — EER tập đóng</t>
+  </si>
+  <si>
+    <t>KHỐI 3 — AUC tập mở</t>
   </si>
 </sst>
 </file>
@@ -256,7 +256,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,14 +287,8 @@
         <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFE2EFDA"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -341,6 +335,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -357,9 +364,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -380,12 +384,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -658,87 +667,87 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -746,12 +755,12 @@
     </row>
     <row r="22" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +783,7 @@
   <sheetData>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -834,14 +843,14 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="21"/>
+      <c r="A10" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="18"/>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
@@ -862,170 +871,170 @@
         <v>12</v>
       </c>
       <c r="H11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="J11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="K11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K11" s="4" t="s">
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="9">
+      <c r="B12" s="8">
         <v>7.9200000000000007E-2</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="8">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <v>0.2</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="8">
         <v>6.25E-2</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="8">
         <v>5.8299999999999998E-2</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="8">
         <v>0.18329999999999999</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="9">
         <f>IFERROR(AVERAGE(B12:G12),"")</f>
         <v>0.10833333333333334</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="9">
         <f>IFERROR(STDEV(B12:G12),"")</f>
         <v>6.5128938780442819E-2</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="10">
         <f>IFERROR(AVERAGE(B12:G12)*100,"")</f>
         <v>10.833333333333334</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="10">
         <f>IFERROR(STDEV(B12:G12)*100,"")</f>
         <v>6.5128938780442818</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="9">
+      <c r="A13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="8">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="8">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="8">
         <v>0.2</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="8">
         <v>0.05</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="8">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="8">
         <v>0.2</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="9">
         <f>IFERROR(AVERAGE(B13:G13),"")</f>
         <v>0.10835</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="9">
         <f>IFERROR(STDEV(B13:G13),"")</f>
         <v>7.1285812052609768E-2</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="10">
         <f>IFERROR(AVERAGE(B13:G13)*100,"")</f>
         <v>10.835000000000001</v>
       </c>
-      <c r="K13" s="11">
+      <c r="K13" s="10">
         <f>IFERROR(STDEV(B13:G13)*100,"")</f>
         <v>7.1285812052609767</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="9">
+      <c r="A14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="8">
         <v>0.1333</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="8">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <v>0.25</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="8">
         <v>0.1333</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="8">
         <v>0.1167</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="8">
         <v>0.18329999999999999</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="9">
         <f>IFERROR(AVERAGE(B14:G14),"")</f>
         <v>0.14721666666666669</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="9">
         <f>IFERROR(STDEV(B14:G14),"")</f>
         <v>6.2718367857164961E-2</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="10">
         <f>IFERROR(AVERAGE(B14:G14)*100,"")</f>
         <v>14.721666666666669</v>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="10">
         <f>IFERROR(STDEV(B14:G14)*100,"")</f>
         <v>6.2718367857164958</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="9">
+      <c r="A15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="8">
         <v>0.26669999999999999</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="8">
         <v>0.19170000000000001</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <v>0.2</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="8">
         <v>0.1958</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="8">
         <v>0.2</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="8">
         <v>0.33329999999999999</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="9">
         <f>IFERROR(AVERAGE(B15:G15),"")</f>
         <v>0.23124999999999998</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="9">
         <f>IFERROR(STDEV(B15:G15),"")</f>
         <v>5.7349690496113485E-2</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="10">
         <f>IFERROR(AVERAGE(B15:G15)*100,"")</f>
         <v>23.125</v>
       </c>
-      <c r="K15" s="11">
+      <c r="K15" s="10">
         <f>IFERROR(STDEV(B15:G15)*100,"")</f>
         <v>5.7349690496113483</v>
       </c>
@@ -1034,12 +1043,12 @@
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>2</v>
@@ -1060,170 +1069,170 @@
         <v>12</v>
       </c>
       <c r="H19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="J19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="K19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K19" s="4" t="s">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="9">
+      <c r="B20" s="8">
         <v>3.4099999999999998E-2</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="8">
         <v>1.41E-2</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="8">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="8">
         <v>3.2199999999999999E-2</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="8">
         <v>2.07E-2</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="8">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="9">
         <f>IFERROR(AVERAGE(B20:G20),"")</f>
         <v>2.2366666666666663E-2</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="9">
         <f>IFERROR(STDEV(B20:G20),"")</f>
         <v>8.6597151608275615E-3</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="10">
         <f>IFERROR(AVERAGE(B20:G20)*100,"")</f>
         <v>2.2366666666666664</v>
       </c>
-      <c r="K20" s="11">
+      <c r="K20" s="10">
         <f>IFERROR(STDEV(B20:G20)*100,"")</f>
         <v>0.86597151608275613</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="9">
+      <c r="A21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8">
         <v>3.1699999999999999E-2</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="8">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="8">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="8">
         <v>3.6799999999999999E-2</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="8">
         <v>3.4799999999999998E-2</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="8">
         <v>3.1699999999999999E-2</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="9">
         <f>IFERROR(AVERAGE(B21:G21),"")</f>
         <v>2.8333333333333335E-2</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="9">
         <f>IFERROR(STDEV(B21:G21),"")</f>
         <v>8.6127037953633682E-3</v>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="10">
         <f>IFERROR(AVERAGE(B21:G21)*100,"")</f>
         <v>2.8333333333333335</v>
       </c>
-      <c r="K21" s="11">
+      <c r="K21" s="10">
         <f>IFERROR(STDEV(B21:G21)*100,"")</f>
         <v>0.86127037953633678</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="9">
+      <c r="A22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8">
         <v>3.39E-2</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="8">
         <v>1.8499999999999999E-2</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <v>1.8499999999999999E-2</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="8">
         <v>4.87E-2</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="8">
         <v>3.5099999999999999E-2</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="8">
         <v>3.1699999999999999E-2</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="9">
         <f>IFERROR(AVERAGE(B22:G22),"")</f>
         <v>3.106666666666667E-2</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="9">
         <f>IFERROR(STDEV(B22:G22),"")</f>
         <v>1.1414668924969588E-2</v>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="10">
         <f>IFERROR(AVERAGE(B22:G22)*100,"")</f>
         <v>3.1066666666666669</v>
       </c>
-      <c r="K22" s="11">
+      <c r="K22" s="10">
         <f>IFERROR(STDEV(B22:G22)*100,"")</f>
         <v>1.1414668924969589</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="9">
+      <c r="A23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="8">
         <v>0.154</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="8">
         <v>0.1245</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="8">
         <v>0.21049999999999999</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="8">
         <v>0.21049999999999999</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="8">
         <v>0.21049999999999999</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="8">
         <v>0.1404</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="9">
         <f>IFERROR(AVERAGE(B23:G23),"")</f>
         <v>0.17506666666666668</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="9">
         <f>IFERROR(STDEV(B23:G23),"")</f>
         <v>3.9922758755710636E-2</v>
       </c>
-      <c r="J23" s="11">
+      <c r="J23" s="10">
         <f>IFERROR(AVERAGE(B23:G23)*100,"")</f>
         <v>17.506666666666668</v>
       </c>
-      <c r="K23" s="11">
+      <c r="K23" s="10">
         <f>IFERROR(STDEV(B23:G23)*100,"")</f>
         <v>3.9922758755710634</v>
       </c>
@@ -1232,12 +1241,12 @@
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>2</v>
@@ -1258,132 +1267,132 @@
         <v>12</v>
       </c>
       <c r="H27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I27" s="4" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" s="9">
+      <c r="A28" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="8">
         <v>0.96499999999999997</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="8">
         <v>0.9889</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="8">
         <v>0.8972</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="8">
         <v>0.99560000000000004</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="8">
         <v>0.99329999999999996</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="8">
         <v>0.93830000000000002</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="9">
         <f>IFERROR(AVERAGE(B28:G28),"")</f>
         <v>0.96304999999999996</v>
       </c>
-      <c r="I28" s="10">
+      <c r="I28" s="9">
         <f>IFERROR(STDEV(B28:G28),"")</f>
         <v>3.8975312699194603E-2</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B29" s="9">
+      <c r="A29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="8">
         <v>0.98440000000000005</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="8">
         <v>0.99280000000000002</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="8">
         <v>0.89170000000000005</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="8">
         <v>0.99439999999999995</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="8">
         <v>0.99</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="8">
         <v>0.90610000000000002</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="9">
         <f>IFERROR(AVERAGE(B29:G29),"")</f>
         <v>0.95990000000000009</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="9">
         <f>IFERROR(STDEV(B29:G29),"")</f>
         <v>4.7591175652635417E-2</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" s="9">
+      <c r="A30" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="8">
         <v>0.9617</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="8">
         <v>0.98829999999999996</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="8">
         <v>0.85940000000000005</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="8">
         <v>0.96279999999999999</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="8">
         <v>0.97670000000000001</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="8">
         <v>0.91220000000000001</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="9">
         <f>IFERROR(AVERAGE(B30:G30),"")</f>
         <v>0.94351666666666667</v>
       </c>
-      <c r="I30" s="10">
+      <c r="I30" s="9">
         <f>IFERROR(STDEV(B30:G30),"")</f>
         <v>4.871449134155733E-2</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" s="9">
+      <c r="A31" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="8">
         <v>0.81940000000000002</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="8">
         <v>0.90610000000000002</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="8">
         <v>0.87939999999999996</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="8">
         <v>0.89610000000000001</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="8">
         <v>0.92330000000000001</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="8">
         <v>0.75780000000000003</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="9">
         <f>IFERROR(AVERAGE(B31:G31),"")</f>
         <v>0.86368333333333336</v>
       </c>
-      <c r="I31" s="10">
+      <c r="I31" s="9">
         <f>IFERROR(STDEV(B31:G31),"")</f>
         <v>6.2965813475779578E-2</v>
       </c>
@@ -1422,205 +1431,205 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="20"/>
+      <c r="B2" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="21"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="G3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>52</v>
-      </c>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="12">
+      <c r="A4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="11">
         <f>IFERROR(Nhap_tung_vong!H28,"")</f>
         <v>0.96304999999999996</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="12">
         <f>IFERROR(Nhap_tung_vong!J12,"")</f>
         <v>10.833333333333334</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <f>IFERROR(Nhap_tung_vong!K12,"")</f>
         <v>6.5128938780442818</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <f>IFERROR(Nhap_tung_vong!J20,"")</f>
         <v>2.2366666666666664</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="13">
         <v>0.995</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="14">
         <v>1.39</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="14">
         <v>2.4</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="14">
         <v>0.34</v>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="15">
         <f>IFERROR(C4-G4,"")</f>
         <v>9.4433333333333334</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="12">
+      <c r="A5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="11">
         <f>IFERROR(Nhap_tung_vong!H29,"")</f>
         <v>0.95990000000000009</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="12">
         <f>IFERROR(Nhap_tung_vong!J13,"")</f>
         <v>10.835000000000001</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <f>IFERROR(Nhap_tung_vong!K13,"")</f>
         <v>7.1285812052609767</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <f>IFERROR(Nhap_tung_vong!J21,"")</f>
         <v>2.8333333333333335</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="13">
         <v>0.99399999999999999</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="14">
         <v>2.5</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="14">
         <v>3.26</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="14">
         <v>0.12</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="15">
         <f>IFERROR(C5-G5,"")</f>
         <v>8.3350000000000009</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="12">
+      <c r="A6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="11">
         <f>IFERROR(Nhap_tung_vong!H30,"")</f>
         <v>0.94351666666666667</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="12">
         <f>IFERROR(Nhap_tung_vong!J14,"")</f>
         <v>14.721666666666669</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <f>IFERROR(Nhap_tung_vong!K14,"")</f>
         <v>6.2718367857164958</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <f>IFERROR(Nhap_tung_vong!J22,"")</f>
         <v>3.1066666666666669</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="13">
         <v>0.99099999999999999</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="14">
         <v>3.4</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="14">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="14">
         <v>0.34</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="15">
         <f>IFERROR(C6-G6,"")</f>
         <v>11.321666666666669</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="A7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="11">
         <f>IFERROR(Nhap_tung_vong!H31,"")</f>
         <v>0.86368333333333336</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="12">
         <f>IFERROR(Nhap_tung_vong!J15,"")</f>
         <v>23.125</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <f>IFERROR(Nhap_tung_vong!K15,"")</f>
         <v>5.7349690496113483</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <f>IFERROR(Nhap_tung_vong!J23,"")</f>
         <v>17.506666666666668</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="13">
         <v>0.9</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="14">
         <v>21.11</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="14">
         <v>5.61</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="14">
         <v>15.86</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="15">
         <f>IFERROR(C7-G7,"")</f>
         <v>2.0150000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
+      <c r="A9" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
